--- a/validation/hand_labels_worksheet.xlsx
+++ b/validation/hand_labels_worksheet.xlsx
@@ -2,24 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="33960" yWindow="-160" windowWidth="30240" windowHeight="20780" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hand-coding" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rubric reference" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAST_TRACK" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hand-coding" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rubric reference" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,20 +28,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE7CE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -54,12 +79,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF888888"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF888888"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -80,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -106,9 +146,28 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -471,139 +530,991 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hand-coding instructions</t>
-        </is>
-      </c>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>FAST TRACK — 22 conversations left, sorted shortest-first. Aim ~30 sec/conv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>1. Go to the 'Hand-coding' tab and read each conversation in column C.</t>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Decision rules (matches your 0/2 pattern):</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2. For each row, fill the 5 yellow score columns (D-H):</t>
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AC  = 2 if user asks for finished answers ("write me…", "give me X"); 0 if asks for explanation/help.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - answer_copying, no_elaboration, no_questioning: 0, 1, or 2</t>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NE  = 2 if user accepts and requests next deliverable; 0 if user builds on / paraphrases.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - no_error_correction, verbatim_reuse: 0, 1, 2, or NA</t>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEC = NA (default for UltraChat). Only mark 0/2 if you see a clear AI error.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>3. The 'Rubric reference' tab has the scoring anchors. The full rubric is in rubric.md at the project root.</t>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NQ  = 2 if user never asks WHY / HOW / WHAT IF; 0 if user probes reasoning.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>4. The 'aggregate (auto)' column auto-computes mean over numeric scores (NA is excluded).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>5. Use the 'notes' column for ambiguous cases. These help the writeup later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Tips:</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Score the USER's behavior, not the assistant's.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - When unsure between two scores, default to the LOWER integer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Try to label all 30 in one sitting; drift across days is real.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Don't look at the LLM-grader scores until you're done (they're in the JSONL files in results/cross_judge_ultrachat/, but ignore them while labeling).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>When done:</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Save (Cmd+S) — the .xlsx already retains your scores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - To compute kappa vs each LLM judge, export this sheet to validation/human_labels.csv with the columns:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       id, answer_copying, no_elaboration, no_error_correction, no_questioning, verbatim_reuse, notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Then run the validate.py commands in the README.</t>
-        </is>
-      </c>
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  VR  = 2 if user copies AI text or says "I'll use that"; NA if no comparable own-text appears; 0 if paraphrases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>n_turns</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>len_chars</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>conversation (USER full / AI truncated)</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>NEC</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>VR</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="240" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>1512</v>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>USER: Write a JavaScript function that takes in one parameter and checks if that parameter is a perfect square. The function should return a boolean value - true if the parameter is a perfect square and false otherwise. You should test your function using a range of inputs and provide the output for each test case.
+  → AI (406 chars): ```
+function isPerfectSquare(num) {
+  if (num &lt; 0) {
+    return false;
+  }
+  else if (Math.sqrt(num) === Math.floor(Math  […truncated]
+USER: Great, the function looks good! Can you add some comments to explain what each line of code is doing?
+  → AI (695 chars): Sure, here is the updated function with comments:
+```
+function isPerfectSquare(num) {
+  if (num &lt; 0) { // check if the   […truncated]</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="240" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>2722</v>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>USER: A family biography, of the royalty of British stage and screen. Hardcover with dust jacket. Remainder mark. Can you use style transfer to rewrite the description of the book in a more poetic or descriptive language?
+  → AI (440 chars): The tome that lies before us is an unparalleled tribute to the dynastic lineage of British theatrical and cinematic exce  […truncated]
+USER: Can you use style transfer to give a new and interesting summary of a chapter from the book?
+  → AI (855 chars): Certainly! Using style transfer, allow me to offer a new and thrilling summary of a chapter from the illustrious book.
+  […truncated]
+USER: Can you use style transfer to give a poetic summary of another chapter from the book? Maybe "A Legacy of Brilliance"?
+  → AI (1003 chars): Certainly! Using style transfer, I present to you a poetic summary of the chapter "A Legacy of Brilliance."
+In "A Legac  […truncated]</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="14" t="n"/>
+      <c r="J12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="240" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>2826</v>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>USER: Given the text: Everything's bigger in Texas. Claim a bigger stake.
+Texas has a long and proud history of citizen involvement in establishing, influencing, and supporting the government.
+So how exactly can you become more involved as a citizen of this state?
+Observe politics in action. You can observe lawmaking from the House and Senate galleries. The architecture of the Capitol reflects the openness of the state business conducted inside. Stroll its wide corridors and open rotunda and view historic paintings, sculptures, and photographs.
+Vote in local and state-wide elections. Register to vote, research issues you care about, learn about where your local and state-level officials stand on those issues, and then head to the polls!
+Learn how Texas's past shapes our state's present and future by visiting the Bullock Texas State History Museum, located at 1800 Congress Avenue, just three blocks north of the Capitol.
+Share your Texas story with the Texas Story Project. Texas history doesn't just belong to the textbooks. You are Texas history, and we want to hear your story.
+How can you become more involved in Texas's government as a citizen?
+  → AI (530 chars): You can become more involved in Texas's government as a citizen by observing politics in action by visiting the House an  […truncated]
+USER: Can you help me register to vote for the upcoming local election in texas? can I do it online or do I need to do it in person?
+  → AI (802 chars): Sure, I'd be happy to help you! In Texas, you can register to vote online, by mail or in person. Here's how you can regi  […truncated]
+USER: Can you provide me with the address of the Texas State Capitol so I can plan a visit to the House and Senate galleries?
+  → AI (94 chars): Yes, of course! The address of the Texas State Capitol is 1100 Congress Ave, Austin, TX 78701.</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="14" t="n"/>
+      <c r="J13" s="15" t="n"/>
+    </row>
+    <row r="14" ht="240" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>2851</v>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>USER: Is it possible to have a combination of drawers, cupboards, and wine racks in the same sideboard?: Hand Made any size, any combination or drawers, cupboards, shelving, glazed, solid doors, wine racks.
+Stunning Oak top shown here but can be made with pine, Reclaimed Timber, Driftwood, Rustic Plank and beech tops also.
+4 Door Oslo sideboard as shown from £815. Can be made any size with your combination of drawers, cupboards, wine racks, shelving, door and plinth styles available, choice of different worktops (shown here with 20mm bull nose oak top) and finished in any Farrow and Ball colour of your choice.
+n.b prices are correct as of 01-05/16 but may be subject to change – please contact us for a quote based on your requirements, sizes and needs.
+  → AI (412 chars): Yes, it is possible to have a combination of drawers, cupboards, and wine racks in the same sideboard. The Hand Made sid  […truncated]
+USER: Can you provide me with the contact information of the seller of the Hand Made sideboard? I would like to request a quote based on my specific needs and requirements.
+  → AI (409 chars): I do not have access to specific information about sellers or their contact details. However, if you have seen this side  […truncated]
+USER: Can you provide me with some examples of the different worktops available for the Hand Made sideboard?
+  → AI (1007 chars): Certainly, here are some examples of the different worktops available for the Hand Made sideboard:
+1. Oak - this is a c  […truncated]</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="14" t="n"/>
+      <c r="J14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="240" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>3680</v>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>USER: Can you provide examples of gratitude prompts that might be useful for daily journaling?
+  → AI (772 chars): Sure, here are a few gratitude prompts for daily journaling:
+1. What three things are you grateful for today?
+2. What   […truncated]
+USER: I struggle with finding things to be grateful for sometimes, so these prompts will be really helpful. Do you have any other tips for cultivating a daily gratitude practice?
+  → AI (1225 chars): Yes, I have a few tips for cultivating a daily gratitude practice:
+1. Set aside time each day: Schedule a specific time  […truncated]
+USER: These tips are great, but what if I don't feel grateful for anything in my life? What can I do then?
+  → AI (1323 chars): If you don't feel grateful for anything in your life, it can be helpful to start by focusing on the small things. Someti  […truncated]</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n"/>
+      <c r="J15" s="15" t="n"/>
+    </row>
+    <row r="16" ht="240" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>4287</v>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>USER: Stitching headlights through the scene.
+today it’s pushing orange through a sieve of suffering grey.
+So that’s two in a row which, though it doesn’t constitute a commitment of any sort from the writer, demonstrates at least some ability to follow through.
+Today I woke William just after 6, to get ready for school, and then sat down to write this poem. He dressed and ate, and then came over with his toothbrush in his mouth, and looked at the sunrise and said "Wooglw!".
+I could write a poem about the view from this flat every day. Can you continue the poem about the view from a flat that the writer mentioned?
+  → AI (656 chars): The view from this flat is ever-changing,
+A canvas painted with the hues of the sky.
+Some days it's an explosion of fier  […truncated]
+USER: Can you find any other instances of the writer using descriptive language to portray the view from the flat?
+  → AI (698 chars): Certainly! Here are some other examples of descriptive language used by the writer to portray the view from the flat:
+-  […truncated]
+USER: Can you suggest any other descriptive words or phrases the writer could use to convey the view from their flat?
+  → AI (927 chars): Certainly! Here are some other descriptive words or phrases the writer could use to convey the view from their flat:
+-   […truncated]
+USER: Can you suggest any other ways the writer could describe the sunrise from their flat?
+  → AI (1088 chars): Certainly! Here are some other ways the writer could describe the sunrise from their flat:
+- The sun rises like a glowi  […truncated]</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
+      <c r="J16" s="15" t="n"/>
+    </row>
+    <row r="17" ht="240" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>4381</v>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>USER: Could you explore in more detail how one would go about comparing financial performance side-by-side or exploring individual companies using Company REFS online? Answer according to: Do you need valuation data for a listed company? Company REFS online is now freely available to ICAEW members. You can compare financial performance side-by-side or explore individual companies in more detail.
+  → AI (1502 chars): To compare financial performance side-by-side or explore individual companies using Company REFS online, ICAEW members c  […truncated]
+USER: Can you show me how to generate custom reports on Company REFS online?
+  → AI (1123 chars): I do not have access to company refs online or any other online services. However, I can provide you with general steps   […truncated]
+USER: Can you guide me on how to access the valuation metrics on Company REFS online?
+  → AI (1215 chars): Sure, here are the steps to access the valuation metrics on Company REFS online:
+1. Log in to your Company REFS online   […truncated]</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="15" t="n"/>
+    </row>
+    <row r="18" ht="240" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>4385</v>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>USER: How did the Spanish conquest of the Low Countries in the 16th century impact European politics and culture?
+  → AI (1539 chars): The Spanish conquest of the Low Countries in the 16th century had a significant impact on European politics and culture.  […truncated]
+USER: Wow, it's interesting how one event had such a ripple effect. Did the Spanish conquest have any lasting effects on the Low Countries themselves?
+  → AI (1314 chars): Yes, the Spanish conquest had several lasting effects on the Low Countries:
+1. Economic decline: The Spanish conquest l  […truncated]
+USER: It's amazing how history can have such a lasting impact on a country. Do you think the Dutch culture and language would be different today if the Spanish hadn't conquered the Low Countries?
+  → AI (1092 chars): It's difficult to speculate on what might have happened had the Spanish not conquered the Low Countries. However, it is   […truncated]</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="240" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>4861</v>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>USER: I’m sure you’ve seen President Trump in the “Sanctions are Coming” meme directed toward Iran.
+Maybe Trump just thought it was cool-looking, or maybe he really is a Game of Thrones fan who imagines himself in combat on the Wall. Or maybe it was just a lower-level staffer on his account who thought it was cool. But regardless, it shows that there’s at least some purchase for this kind of heroic-fiction narrative in the White House, shaping how they want the public to think of them and quite possibly how the president thinks about himself.
+Oh come on! Try a bit harder. This has nothing to do with what the cast of Game of Thrones thinks.
+In a statement released by the White House later Friday, Trump said: “On Monday, November 5, the termination of United States participation in the Iran nuclear deal will be complete. The last set of sanctions lifted under the terrible nuclear deal will come back into force, including powerful sanctions on Iran’s energy, shipping, and shipbuilding sectors, and sanctions targeting transactions with the Central Bank of Iran and sanctioned Iranian banks.
+I have a feeling that some executive finally figured out the President Trump, personally and totally for free, gave them the finest advertising any TV show has ever received! Today the entire country is talking about Game of Thrones. I can’t even imagine what that kind of advertising is worth!
+You guys get a ANNOYING BUZZER SOUND HERE for literally looking a gift horse in the mouth!
+Activists like Amy Schumer have used the phrase “November Is Coming” in the wake of the confirmation of Brett Kavanaugh to the Supreme Court, and a jacket featuring the phrase even sold out. But they don’t use the phrase in quite the same manner as Trump did.
+Trump’s administration has used movie marketing tactics in its messaging, and even used an blockbuster-style trailer in Trump’s meeting with Kim Jong Un. Trump said he played it for the North Korean leader.
+Well, close but no cigar but at least they’re awake enough to realize we’ve seen something like this before.
+All right . . . I guess it’s my job to point out what should be obvious to everyone. Donald Trump is using the “Little Rocket Man” strategy to see if he can get Iran to communicate with him. He’s asking them to meme back or tweet something that he can use to start a dialog. He’s put something so outrageous and over the top out there that the leadership of Iran has certainly seen it and probably has analysts working overtime trying to figure out what it means.
+Note to Iran: It just means he’d like to engage with you and humor is always a good way to start a conversation.
+He’s right here — listening. You don’t have to go through any kind of channels. If you want to say something, just say it and we’ll see whether we can talk with one another.
+Good grief. Now was that so hard to understand? Based on the passage above, Could you continue the article's discussion on how the Trump administration has used movie marketing tactics in its messaging?
+  → AI (558 chars): The article suggests that the Trump administration has used movie marketing tactics in its messaging, which includes the  […truncated]
+USER: Can you provide me with more examples showing how the Trump administration has utilized movie marketing tactics in their messaging?
+  → AI (1160 chars): Sure, here are a few more examples of how the Trump administration has used movie marketing tactics in their messaging:
+  […truncated]</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="15" t="n"/>
+    </row>
+    <row r="20" ht="240" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>5551</v>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>USER: How can the integration of IT systems with procurement in supply chains improve product ordering lead times and pricing provisions? Answer according to: Using the Internet, research information technology (IT) systems for supply chains.
+-	Procurement - integration would allow for a clear line of sight into the negotiated terms and conditions, penalties and rewards, lead times for product ordering, as well as the locked pricing and related provisions.
+This 200 word document outlines the cross functional team that Supply Chain would need to consider integrating IT systems with.
+  → AI (1449 chars): The integration of IT systems with procurement in supply chains requires a cross-functional team that involves different  […truncated]
+USER: Can you provide examples of IT systems that are commonly used for supply chain management?
+  → AI (1723 chars): Sure! There are several IT systems that are commonly used for supply chain management. Here are some examples:
+1. Enter  […truncated]
+USER: Can you explain how an ERP system can help organizations with supply chain management?
+  → AI (1621 chars): Sure! Enterprise Resource Planning (ERP) systems can help organizations with supply chain management in several ways. 
+  […truncated]</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="240" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>5661</v>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>USER: Can you explain the organizational structure of the Habsburg imperial court and the roles of various officials?
+  → AI (2352 chars): The Habsburg imperial court was a complex administrative and political organization that played a central role in the go  […truncated]
+USER: Can the Habsburg imperial court officials override each other's decisions if necessary?
+  → AI (1210 chars): The Habsburg imperial court officials had specific roles and responsibilities that were often divided among different de  […truncated]
+USER: So, if there was a conflict between officials, did the emperor always have the final say? Or were there other ways for officials to settle their disputes? And how did the emperor ensure that officials were carrying out their duties effectively?
+  → AI (1657 chars): As the ultimate authority within the court, the emperor of the Habsburg empire had the power to settle disputes between   […truncated]</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="240" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>5730</v>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>USER: How can embedded sensors in clothes reduce health issues and promote wellbeing for individuals?
+  → AI (1178 chars): Embedded sensors in clothes can help reduce health issues and promote wellbeing for individuals by providing continuous   […truncated]
+USER: That sounds great! Can you tell me more about how the embedded sensors work and how they are integrated into clothes?
+  → AI (1366 chars): Yes, of course! Embedded sensors in clothes can work in a few different ways, but they all typically involve sensors tha  […truncated]
+USER: Can embedded sensors in clothes also monitor an individual's mental health and wellbeing? For example, could they detect changes in stress levels or sleep patterns?
+  → AI (1165 chars): Yes, embedded sensors in clothes can definitely monitor an individual's mental health and wellbeing. For example, sensor  […truncated]
+USER: Wow, the potential that embedded sensors in clothes have is incredible. Can you give me some examples of companies or products that are currently utilizing this technology?
+  → AI (1473 chars): Yes! Here are some examples of companies and products that are currently utilizing embedded sensors in clothing:
+1. Ath  […truncated]</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="240" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>USER: What many companies do when planning their global marketing strategies is to organize the world’s countries into three categories.
+Emerging Markets – Markets regarded as having the most potential for growth (e.g. Huge countries such as China and India) and targeted for long-term investment.
+Rest of the World (ROW) Markets – Markets that are often not included in a global marketing strategy because a company does not have sufficient time or resources to pay them any attention.
+A typical company involved in global marketing is likely to have four or five core markets and maybe six to twelve emerging markets.
+Is it Wise to Ignore the ROW?
+Collectively the ROW consists of a huge market of over a billion people. Of course the ROW includes a lot of small countries, but even a country with only five to six million people (e.g. Denmark and Ireland) could be very profitable for the right product. Click here for a list of countries in order of population.
+Which Languages Does the “Rest of the World” Speak?
+The Web Globalization Report Card, which tracks the websites of 150 global companies, reports a steadily increasing number of languages supported by global content. As of 2018, the average number of languages supported by all 150 global websites is now thirty-two.
+The success of global marketing can only be achieved through the use of local languages. If the growth in the number of languages is imagined as a curve, this curve begins quite steeply as companies load up on the core European and Asian languages. After a company reaches the level of twenty languages, the curve starts to taper off. The number of languages supported by a few companies, such as Facebook, Visa, and Dyson has shot up in sudden spikes. However, most companies are only in the early stages of this growth curve.
+It would be a herculean task to utilize the more than 6,000 languages spoken worldwide, so a global marketing company has to narrow down its language choices to the languages spoken by its core target audiences. The following is a list of ten languages that are shared by leading global websites.
+English – English is the language of globalization and is spoken by over 75% of the world’s population.
+Chinese (Simplified) – If people in Chinese speaking markets continue to expand their internet usage, Chinese might one day supplant English as the most widely used internet language.
+Arabic – The Arabic language is spoken by 295 million speakers worldwide, and is the official language of 28 different countries. A report from the British Council ranks Arabic as the second most important language of the future.
+Spanish – There are a number of important Spanish speaking countries, not to mention that the Hispanic population in the US will likely double by 2050.
+German – The German language is the fourth most spoken language in the world with nearly 210 million speakers worldwide.
+Portuguese – Second behind Spanish in Latin America. Portuguese is spoken by 215 million people in Portugal, Brazil, and some parts of Africa.
+French – French is the official language of over 29 countries throughout the world including several of the fastest growing African economies.
+Japanese – Japanese has 130 million native speakers and a similar number of non-native speakers spread out over the world.
+Russian – There are 160 million native speakers in Russia and throughout central and Eastern Europe.
+Hindi – Although India is home to 126 million English speakers, around 85% of the population doesn’t speak English well or at all. India represents an enormous growing market.
+If you are hoping to increase your global marketing reach, it’s essential to expand the number of languages your website or app supports. All countries, including the “rest of the world,” are within your reach. Once you have decided on your target markets, Localize will help you translate your content into the local languages. Talk to us for more information.
+Can you provide a list of the top ten languages that global marketing companies should focus on, according to the leading global websites?
+  → AI (259 chars): Yes, here is a list of the top ten languages that global marketing companies should focus on, according to the leading g  […truncated]
+USER: Can you please provide me with more details on how companies can effectively target emerging markets?
+  → AI (1761 chars): Certainly! Here are some tips on how companies can effectively target emerging markets:
+1. Conduct Market Research: Bef  […truncated]</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="15" t="n"/>
+    </row>
+    <row r="24" ht="240" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>6474</v>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>USER: Identify at least 5 different types of natural disasters and analyze how the increasing global temperature affects their frequency and intensity. Provide at least 3 examples of regions or communities that have been severely impacted by these changes in the past decade. Use credible sources and statistics to support your analysis.
+  → AI (2666 chars): 1) Hurricanes and tropical storms are intensified by warming ocean temperatures, as warm water provides energy for the s  […truncated]
+USER: This is a great analysis of how the increasing global temperature affects natural disasters. Could you provide more information on how wildfires are specifically affected by climate change, such as how higher temperatures and changing rainfall patterns contribute to their frequency and intensity?
+  → AI (1514 chars): Certainly, here is more information on how climate change specifically affects wildfires:
+1) Higher temperatures and dr  […truncated]
+USER: Thank you for providing me with such detailed information on how wildfires are affected by climate change. Can you please provide me with some statistics on how many wildfires have occurred globally in the past decade and how much damage has been caused by them? Additionally, how do these numbers compare to historical wildfire trends?
+  → AI (1330 chars): Certainly! Here are some statistics on global wildfires over the past decade:
+1) According to data from the Global Fore  […truncated]</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="240" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>6807</v>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>USER: ❶Writers Experienced writers with the highest satisfaction rates.
+Lots of people wonder if striving for excellent grades in college affects the rest of their life at all. Which is more likely to make you a millionaire? If a college degree costs a fortune and sometimes has a questionable ROI, you might be tempted to forego school and play the lottery instead. Should College Education be Free? One of the most expensive things most people will ever pay for is a college education.
+Gone are the days when people could live comfortably with a high school education, and the competition for jobs is fierce. How to Stay Happy in the Cold Season. Fall is almost upon us, and with that comes the shortening of days and frigidity in the air.
+Gone are those long, hot, and sunny summer days, and people are often left depressed in its wake. Comprehensive reviews combined with consistent feedback allow us to make sure our staff delivers great papers, without fail.
+Once you buy custom essay from us, you get access to your customer profile, real-time order tracking and messaging system. We operate non-stop so you can get the help you need anytime. Some may also be new in the field. If you add this to inadequate research, the final paper that you create might not meet the expected standards.
+The huge workload that students have to deal with is another impediment to writing a presentable paper. Imagine a situation where you have to handle loads of writing assignments from your instructors, attend classes as required and still write the essay.
+With all the work, the student may not have time to prepare and write a good essay. Furthermore, writing essays may sometimes seem boring to students. They see their colleagues enjoying their free time and feel that the work may be preventing them from doing what they love. They end up postponing the work until it is late and the deadline for submission is almost reaching. As a result, they may end up writing a poor paper or failing to submit the paper on time. The consequences may be dire, ranging from receiving a poor grade to getting penalized.
+There are online essay writer agencies out there that claim they can help students with writing their essays. However, most of them are just trying to make money from unsuspecting students. They either produce plagiarized essays or in some cases do not deliver any paper at all.
+In other circumstances, they leak out your information to unauthorized individuals putting your further academic career at risk. When your instructor knows that you were assisted in writing the essay, you can even be discontinued from your course.
+Such a turn of events may be very devastating. Fortunately, you do not have to go through all these problems when decided to rely on our company.
+You already have too many things to handle. All these engagements that may not be related to your essay may have a negative bearing on the quality of the essays you write.
+We are ready to get the burden off your back and make your academic life easier. One of the benefits of hiring our services is that we provide high-quality papers. Our writers ensure that your papers meet the quality standards expected. With our custom essay writing service, we aim at satisfying the needs of the clients. The essay you receive is properly formatted, the language used is appropriate, the topic has been researched properly, and the overall outlook of the paper is impressive.
+Producing a quality paper begins by following the instructions. Before we start writing your essay, we first look at the instructions that you have issued. They are thoroughly assessed such that when the essay is finally completed, you can confidently say that the paper meets all of the requirements.
+Thirdly, we ensure timely delivery. In the academic circles, time is an important factor. You must submit the job given within the stipulated timelines. With this in mind, we work hard so that you can receive the paper when you want it. Even if you need the essay on short notice, give us your timeline, and we are glad to deliver. Depending on the topic, the education level and the topic of your paper, we deliver within 3 hours to 5 days.
+What are the risks of hiring other online essay writer agencies, and how does your company ensure student privacy and academic integrity?
+  → AI (848 chars): The risks of hiring other online essay writer agencies are numerous. Some may provide plagiarized work, leak your inform  […truncated]
+USER: Can you provide me with more information on how your writers ensure the quality of the papers they write? I want to make sure that I am getting a top-notch essay.
+  → AI (1478 chars): Absolutely! Our writers follow a strict process to ensure the quality of the papers they write. Here is a breakdown of o  […truncated]</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="14" t="n"/>
+      <c r="J25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="240" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>7099</v>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>USER: Write a 500-word fictional story in third person omniscient point of view about a middle-aged man named Tom who sets out for a solo hike in the Appalachian Mountains, but gets lost due to a sudden storm. Incorporate themes of survival, resourcefulness, and inner strength in the story. Use vivid descriptions and sensory details to create an atmospheric setting and build tension. End the story with a realistic resolution that reflects the character's growth and transformation.
+  → AI (2712 chars): Tom had always been a man of solitude. He cherished the moments he spent in the great outdoors, away from the hustle and  […truncated]
+USER: This story is a good start, but I'd like to know more about Tom's background. Can you add some information about his life before he went on this hike?
+  → AI (1451 chars): Tom had always been a wanderer, never really fitting in with the norms of society. He had worked a number of odd jobs th  […truncated]
+USER: That's great! Can you add some more sensory details to the story, like how Tom feels and what he sees, smells, and hears during the storm?
+  → AI (2169 chars): As Tom stumbled through the wilderness, he was buffeted by the winds and pelted by rain that felt like small stones hitt  […truncated]</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="n"/>
+      <c r="I26" s="14" t="n"/>
+      <c r="J26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="240" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>8002</v>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>USER: Write a compelling fictional story with well-defined characters and an engaging plot that demonstrates the transformative power of hope. Use imagery and descriptive language to convey the emotions of your characters and tug at the heartstrings of your readers. Show how a single glimmer of hope can light up even the darkest of situations, and leave your readers feeling inspired and empowered. Pay close attention to pacing and structure to ensure that your story is both satisfying and impactful.
+  → AI (2234 chars): Lauren had always been a fighter. When she was just 10 years old, she lost her father to cancer, and her mother struggle  […truncated]
+USER: I really like the storyline, but I feel like it could use more descriptive language to really convey the emotions of the characters. Can you add more imagery to bring the story to life?
+  → AI (2266 chars): Lauren had always known the power of hope, but it wasn't until her mother's illness that she truly understood its transf  […truncated]
+USER: This is a great start, but I feel like the story could benefit from more sensory details to really immerse the reader in the setting. Could you add some more descriptions of the hospital environment, like the smell of antiseptic or the hum of machines, to create a more vivid picture for the reader?
+  → AI (2520 chars): Lauren stood at the entrance of the hospital, steeling herself for another day of soul-numbing routine. As she stepped i  […truncated]</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="n"/>
+      <c r="I27" s="14" t="n"/>
+      <c r="J27" s="15" t="n"/>
+    </row>
+    <row r="28" ht="240" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>8235</v>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>USER: What are the classic cocktails that every bartender should know how to make and what are their ingredients?
+  → AI (1071 chars): 1. Old Fashioned: Ingredients- bourbon or rye whiskey, sugar, bitters, ice, orange twist or cherry for garnish.
+2. Marti  […truncated]
+USER: I've had all of these classic cocktails, but I'm looking for something new to try. Do you have any recommendations?
+  → AI (1130 chars): Sure, here are a few modern cocktail recommendations to try:
+1. Elderflower Sour: Ingredients- gin, elderflower liqueur  […truncated]
+USER: The Elderflower Sour sounds interesting. I love trying new cocktails with unique ingredients.
+  → AI (219 chars): The Elderflower Sour is a great cocktail that offers a nice balance of sweetness and sourness. I hope you enjoy it! If y  […truncated]
+USER: Definitely going to try the Elderflower Sour tonight! Do you have any other unique cocktail recommendations with interesting flavors? I'm in the mood to experiment.
+  → AI (1107 chars): Sure, here are a few more unique cocktail recommendations:
+1. The Last Word: Ingredients- gin, lime juice, green chartr  […truncated]
+USER: The Smoked Maple Old Fashioned sounds intriguing. How exactly do you use a smoking gun in a cocktail?
+  → AI (799 chars): To use a smoking gun in a cocktail like the Smoked Maple Old Fashioned, you'll need a handheld smoker or smoking gun. He  […truncated]
+USER: Wow, I never knew you could use a smoking gun in cocktails. That's a really cool technique! I can't wait to try it out with the Smoked Maple Old Fashioned. Do you have any other creative cocktail techniques that I should know about?
+  → AI (1383 chars): Yes, there are several creative cocktail techniques that can add unique flavors and textures to your drinks. Here are a   […truncated]
+USER: Wow, these techniques are really cool! I've never heard of fat-washing before. I might have to try that with bacon and bourbon. Do you have any tips for getting the proportions right?
+  → AI (1531 chars): Fat-washing is a fun technique that can add a unique savory flavor to your cocktails. Here are a few tips for getting th  […truncated]</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="15" t="n"/>
+    </row>
+    <row r="29" ht="240" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>8366</v>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>USER: How can smart building automation systems be used to improve the experience of building users?
+  → AI (1583 chars): Smart building automation systems can be used to improve the experience of building users in several ways:
+1. Comfort:   […truncated]
+USER: Can smart building automation systems also help with maintenance and upkeep of the building?
+  → AI (1168 chars): Yes, smart building automation systems can help with maintenance and upkeep of the building in several ways:
+1. Predict  […truncated]
+USER: Wow, it sounds like smart building automation systems have a lot of benefits for both occupants and maintenance personnel. Can you give me an example of a building that successfully utilizes these systems?
+  → AI (1459 chars): Certainly! One example of a building that successfully utilizes smart building automation systems is the Edge in Amsterd  […truncated]
+USER: That's impressive! Can smart building automation systems also make coffee for users? I mean, that would really take the building experience to the next level.
+  → AI (929 chars): It is possible for smart building automation systems to make coffee for users, but it would require additional equipment  […truncated]
+USER: Hey, can the automated system also play my favorite music in the office? That would be really cool, don't you think?
+  → AI (745 chars): Yes, the automated system in a smart building can also play your favorite music in the office, making your working envir  […truncated]
+USER: This is all so fascinating! Can smart building automation systems also order me lunch from my favorite restaurant? That would be a real time-saver!
+  → AI (629 chars): Yes, smart building automation systems can also help users order food from their favorite restaurants, usually via food   […truncated]
+USER: Can the automation system also order me a massage during my break time? A quick massage would really help me relax and recharge for the rest of the workday.
+  → AI (885 chars): It's possible for a smart building automation system to facilitate booking a massage during break time, but this type of  […truncated]</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="15" t="n"/>
+    </row>
+    <row r="30" ht="240" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>8919</v>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>USER: Design a clear and concise product feature announcement email that highlights the benefits of the new feature for the customers. Use visually appealing graphics and make the email easy to scan with bullet points and headings. Don't forget to include a call-to-action and a way for customers to provide feedback or ask questions. Once the email is drafted, distribute it to all customers through the company's preferred email communication platform.
+  → AI (1504 chars): Subject: Introducing Our New Product Feature – Experience Better Functionality and Efficiency!
+Dear Valued Customers,
+  […truncated]
+USER: This looks good, but can you add some more visuals to the email? Maybe some screenshots of the new features in action?
+  → AI (1734 chars): Of course! Here's an updated version of the email with additional screenshots:
+Subject: Introducing Our New Product Fea  […truncated]
+USER: This looks great! Can you also include some details on how to access the new feature and any tutorials or resources available to help us make the most of it?
+  → AI (2016 chars): Absolutely! Here's an updated version of the email with more details on accessing the new feature and related resources:  […truncated]
+USER: This email looks fantastic! Can you add some more information about the benefits of each of the new features? I want to make sure I understand exactly how they will improve my experience with the product.
+  → AI (2738 chars): Sure thing! Here's an updated version of the email with more details on the benefits of each new feature:
+Subject: Intr  […truncated]</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="15" t="n"/>
+    </row>
+    <row r="31" ht="240" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>9734</v>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>USER: Write a 500-word blog post in an informative and engaging style, explaining the benefits of practicing random acts of kindness. Share real-life examples to illustrate the positive impact of small acts of kindness on individuals and communities. Include actionable tips on how readers can incorporate kindness into their daily lives and the benefits they can reap, such as improved mental health, stronger relationships, and a more positive outlook on life. Use research and data to support your claims and provide credible sources for readers who want to learn more about the science behind kindness. Use a clear and concise writing style that is easy to follow and understand for readers of all ages and backgrounds. Finally, conclude the post with a call to action to inspire readers to start practicing kindness today.
+  → AI (3693 chars): As human beings, we all crave kindness in our lives. Whether it is a simple smile from a stranger or a heartfelt gesture  […truncated]
+USER: This is a great blog post! I really enjoyed learning about the benefits of practicing random acts of kindness. Can you give me more information on how exactly kindness improves mental health?
+  → AI (1409 chars): Certainly! There are a few different ways that kindness has been shown to improve mental health:
+1. Release of Oxytocin  […truncated]
+USER: Can you share some specific examples of how performing acts of kindness can release oxytocin in our bodies and promote better mental health? I'm curious to learn more about this aspect.
+  → AI (1627 chars): Certainly! Here are a few examples of how performing acts of kindness can release oxytocin in our bodies and promote bet  […truncated]
+USER: Thanks for providing all of this helpful information on the benefits of practicing kindness! I'm curious to know if there are any other specific actions that have been proven to release oxytocin in the body and promote mental health. Can you give me some more ideas?
+  → AI (1542 chars): Absolutely! Here are some additional actions that have been shown to release oxytocin in the body and promote mental hea  […truncated]</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="240" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>11669</v>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>USER: Write an essay that evaluates the positive and negative influence of social media on personal relationships, citing specific examples and research to support your claims. Analyze the ways in which social media usage affects communication patterns, trust levels, and emotional connections in romantic partnerships, friendships, and family relationships. Consider the role of social comparison, cyberbullying, and privacy concerns in shaping the impact of social media use on personal relationships. Finally, provide recommendations for how individuals can cultivate healthy and meaningful relationships in the age of social media.
+  → AI (4380 chars): Social media is a ubiquitous presence in modern society and has revolutionized the way people communicate with one anoth  […truncated]
+USER: Can you add more information on the impact of social media on family relationships? Also, can you suggest some practical tips on how to balance social media use and face-to-face communication with our loved ones?
+  → AI (2556 chars): Sure, here are some additional details on the impact of social media on family relationships. Social media has transform  […truncated]
+USER: Can you give some examples of "shared activities" that families can do together to strengthen their relationships?
+  → AI (2076 chars): Sure! Here are a few examples of shared activities that families can do together to strengthen their relationships:
+1.   […truncated]
+USER: Can you give some more examples of outdoor activities that families can enjoy together?
+  → AI (1615 chars): Sure, here are some more examples of outdoor activities that families can enjoy together:
+1. Picnics: Going on a picnic  […truncated]</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="15" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"0,1,2"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"0,1,2,NA"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -614,22 +1525,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hand-coding instructions</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1. Go to the 'Hand-coding' tab and read each conversation in column C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2. For each row, fill the 5 yellow score columns (D-H):</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - answer_copying, no_elaboration, no_questioning: 0, 1, or 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - no_error_correction, verbatim_reuse: 0, 1, 2, or NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>3. The 'Rubric reference' tab has the scoring anchors. The full rubric is in rubric.md at the project root.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>4. The 'aggregate (auto)' column auto-computes mean over numeric scores (NA is excluded).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>5. Use the 'notes' column for ambiguous cases. These help the writeup later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Tips:</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Score the USER's behavior, not the assistant's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - When unsure between two scores, default to the LOWER integer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Try to label all 30 in one sitting; drift across days is real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Don't look at the LLM-grader scores until you're done (they're in the JSONL files in results/cross_judge_ultrachat/, but ignore them while labeling).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>When done:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Save (Cmd+S) — the .xlsx already retains your scores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - To compute kappa vs each LLM judge, export this sheet to validation/human_labels.csv with the columns:</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       id, answer_copying, no_elaboration, no_error_correction, no_questioning, verbatim_reuse, notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Then run the validate.py commands in the README.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="409" customHeight="1"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="7" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="27" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>id</t>
@@ -681,7 +1732,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="360" customHeight="1">
+    <row r="2" ht="409" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>32</t>
@@ -714,18 +1765,32 @@
 1. Choose your text: Start by choosing a piece of writing, such as a poem, song lyrics, or a personal journal entry, that you want to turn into a visual poem. Think about what the words mean to you and how you want to convey that meaning visually. 2. Determine your visual style: Decide on the aesthetic you want your visual poem to have. You could choose to use watercolors, photography, animation, or any other medium that you feel suits the text. 3. Select your imagery: Determine what images and colors best represent the text you have chosen, and how they can convey the message effectively. Consider using symbolism to add further depth to the visual experience. 4. Choose your font: Pick a font style that complements the tone of the text and is legible for viewers. 5. Experiment with layout: Play around with different layouts to showcase the text in new and interesting ways. Consider layering text over images, using varying sizes and spacing, and incorporating graphics. 6. Add audio: Consider adding audio elements such as music or sound effects that enhance the theme or tone of the poem. 7. Edit and refine: Make sure y  […truncated…]</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="6" t="n"/>
-      <c r="H2" s="6" t="n"/>
+      <c r="D2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I2" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D2:H2),D2:H2)), "")</f>
         <v/>
       </c>
-      <c r="J2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3" ht="360" customHeight="1">
+      <c r="J2" s="5" t="n"/>
+    </row>
+    <row r="3" ht="409" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>91</t>
@@ -761,18 +1826,30 @@
 Sure, income inequality has been linked to mental health problems in many Southeast Asian countries. For example, a study on income inequality and mental health in Vietnam found that there is a significant association between income inequality and depressive symptoms among older adults. The study suggested that older adults living in areas with higher levels of income inequality are more likely to experience depressive symptoms. Another study conducted in Indonesia found that income inequality was associated with increased rates of mental health problems, including depression, anxiety, and substance abuse. The study found that individuals living in regions with higher levels of income inequality tend to feel more stressed and face more social pressures, which can negatively impact mental health outcomes. Regarding the impact of tax policies, progressive tax policies aim to tax higher-income earners at a higher rate than lower-income earners. On the other hand, flat tax policies aim to apply a uniform tax rate to all income earners, regardless of their income level. While both tax policies generate revenue for the government, progressive tax policies are generally seen as more effec  […truncated…]</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
+      <c r="D3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I3" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D3:H3),D3:H3)), "")</f>
         <v/>
       </c>
-      <c r="J3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4" ht="360" customHeight="1">
+      <c r="J3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="409" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>49</t>
@@ -813,18 +1890,32 @@
 We can partner with high-end hotels, event halls, and other luxurious locations to host exclusive events for our target audience. These events could be launch parties, fashion shows, trunk sh  […truncated…]</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
+      <c r="D4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I4" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D4:H4),D4:H4)), "")</f>
         <v/>
       </c>
-      <c r="J4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="360" customHeight="1">
+      <c r="J4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="409" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>15</t>
@@ -879,18 +1970,32 @@
 1. Start with day-old bread or fresh bread that has been left out to dry for a few hours. 2. Cut your bread into cubes (about 1 inch) and toss them with olive oil and any desired seasonings like garlic powder or Italian seasoning. 3. Spread the bread evenly on a baking sheet and bake at 350°F for 10-15 minutes, or until they are golden brown and crispy. 4. Let the croutons cool and store them in an airtight container for up to a week. I hope you find these tips helpful! Enjoy your soup!</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+      <c r="D5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I5" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D5:H5),D5:H5)), "")</f>
         <v/>
       </c>
-      <c r="J5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="360" customHeight="1">
+      <c r="J5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="409" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>12</t>
@@ -947,18 +2052,30 @@
 Have fun and enjoy your at-home activities!</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I6" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D6:H6),D6:H6)), "")</f>
         <v/>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="360" customHeight="1">
+      <c r="J6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>46</t>
@@ -984,18 +2101,32 @@
 It was only when Zoey recognized the impact that her addiction was having on her relationships that she was able to seek help and turn her life around. She apologized to her parents and friends, and slowly started to rebuild those relationships brick by brick. And as she did so, she b  […truncated…]</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
+      <c r="D7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I7" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D7:H7),D7:H7)), "")</f>
         <v/>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="360" customHeight="1">
+      <c r="J7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="409" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>48</t>
@@ -1035,18 +2166,30 @@
 5. No  […truncated…]</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
+      <c r="D8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I8" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D8:H8),D8:H8)), "")</f>
         <v/>
       </c>
-      <c r="J8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="360" customHeight="1">
+      <c r="J8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="409" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>18</t>
@@ -1084,18 +2227,30 @@
 4. Attend skydiving events and clinics: attending events and clinics that focus on the specific skills required for each cop can be an excellent way to prepare for the tests. These events often have experi  […truncated…]</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
+      <c r="D9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I9" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D9:H9),D9:H9)), "")</f>
         <v/>
       </c>
-      <c r="J9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="360" customHeight="1">
+      <c r="J9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="409" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>17</t>
@@ -1130,18 +2285,30 @@
 These are just a few examples of the different worktops available, and the options may vary based on the seller's availability and preferences.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="D10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I10" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D10:H10),D10:H10)), "")</f>
         <v/>
       </c>
-      <c r="J10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="360" customHeight="1">
+      <c r="J10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="409" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>4</t>
@@ -1173,18 +2340,32 @@
 1. Picnics: Going on a picnic is a great way to spend time together outdoors while enjoying a meal or snack. Families can pack a basket of their favorite foods and drinks, and find a scenic location in nature, such as a park, beach, or forest. 2. Geocaching: Geocaching is an outdoor treasure hunt that uses GPS coordinates to locate hidden "caches" containing small treasures or messages. Families can work together to discover new caches and share their finds with one another. 3. Nature walks: Taking a leisurely stroll in nature can be a great way to relax and bond as a family. Families can choose a trail or park to explore, and spend time observing and discussing the plants, animals, and natural features they encounter along the way. 4. Water activities: If a family lives near a lake, river, or ocean, they can enjoy activities such as swimming, kayaking, or paddleboarding. These activities provide a fun and exciting challenge that the whole family can enjoy together. 5. Gardening: Gardening is a great way to connect with nature and engage in a productive, creative activity. Families can work t  […truncated…]</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="D11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I11" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D11:H11),D11:H11)), "")</f>
         <v/>
       </c>
-      <c r="J11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="360" customHeight="1">
+      <c r="J11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="409" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>75</t>
@@ -1222,18 +2403,30 @@
 - Global Forest Wa  […truncated…]</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
+      <c r="D12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I12" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D12:H12),D12:H12)), "")</f>
         <v/>
       </c>
-      <c r="J12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="360" customHeight="1">
+      <c r="J12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="409" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>11</t>
@@ -1269,18 +2462,32 @@
 In any event, the Spanish conquest of the Low Countries did have a significant impact on Dutch culture and language, as it led to a sense of resistance and a desire for independence that helped shape the Dutch national identity. The suppression of Dutch culture and language by the Spanish also contributed to the development of a distinct Dutch language and literature, which would have been less likely to emerge if the Dutch had not been oppressed by an outside power.</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I13" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D13:H13),D13:H13)), "")</f>
         <v/>
       </c>
-      <c r="J13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="360" customHeight="1">
+      <c r="J13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="409" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>81</t>
@@ -1338,18 +2545,32 @@
 I hope this helps!</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="D14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I14" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D14:H14),D14:H14)), "")</f>
         <v/>
       </c>
-      <c r="J14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="360" customHeight="1">
+      <c r="J14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="409" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>72</t>
@@ -1384,18 +2605,30 @@
 In addition, the emperor would often rely on a network of spies and informants to keep him informed of the activities of his offici  […truncated…]</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="D15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I15" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D15:H15),D15:H15)), "")</f>
         <v/>
       </c>
-      <c r="J15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="360" customHeight="1">
+      <c r="J15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="409" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>59</t>
@@ -1433,18 +2666,30 @@
 Fourthly, an ERP system can help organizations manage quality control processes and identify potential supply chain risks. This can help organizations   […truncated…]</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="D16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I16" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D16:H16),D16:H16)), "")</f>
         <v/>
       </c>
-      <c r="J16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="360" customHeight="1">
+      <c r="J16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="409" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>23</t>
@@ -1485,18 +2730,32 @@
 5. Hexoskin - Hexoskin makes smart shirts with sensors that track vital signs like heart rate, breathing, and activity levels. The data is sent to a smartphone app, which provides detailed insights  […truncated…]</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="D17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I17" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D17:H17),D17:H17)), "")</f>
         <v/>
       </c>
-      <c r="J17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18" ht="360" customHeight="1">
+      <c r="J17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="409" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>96</t>
@@ -1525,18 +2784,32 @@
 Overall, the Trump administration has sought to use movie marketing tactics to convey a sense of strength, determination, and accomplishment, while shaping the public's perception of the administration and the president.</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="D18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I18" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D18:H18),D18:H18)), "")</f>
         <v/>
       </c>
-      <c r="J18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="360" customHeight="1">
+      <c r="J18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="409" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>56</t>
@@ -1573,18 +2846,30 @@
 Yes, of course! The address of the Texas State Capitol is 1100 Congress Ave, Austin, TX 78701.</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="D19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I19" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D19:H19),D19:H19)), "")</f>
         <v/>
       </c>
-      <c r="J19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="360" customHeight="1">
+      <c r="J19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="409" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>28</t>
@@ -1629,18 +2914,32 @@
 5. Practicing deep breathing: Finally, practicing deep breathing exercises or meditation can also help to release oxytocin in the body. By focusing on our breath and calmi  […truncated…]</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="D20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I20" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D20:H20),D20:H20)), "")</f>
         <v/>
       </c>
-      <c r="J20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="360" customHeight="1">
+      <c r="J20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="409" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>52</t>
@@ -1720,18 +3019,30 @@
 - The sunrise is a daily reminder that no matter what happens in the day ahead, the sun will always rise again tomorrow.</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="D21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I21" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D21:H21),D21:H21)), "")</f>
         <v/>
       </c>
-      <c r="J21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="360" customHeight="1">
+      <c r="J21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="409" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>5</t>
@@ -1770,18 +3081,30 @@
 1. Conduct Market Research: Before entering an emerging market, do your research. Understand the local culture, consumer preferences, and market trends. This information will help you tailor your products and marketing strategies to suit the needs of the local market. 2. Localize Your Marketing: Use local languages, cultural references, and imagery that resonates with the target audience. Avoid direct translations that may not make sense in the local context. 3. Build Local Partnerships: Partner with local businesses, distributors or agents who have industry know-how and established relationships in the local market. This can help overcome regulatory and distribution challenges. 4. Adapt Your Products: Products that are successful in established markets may not be relevant in emerging markets. Conduct market research to understand the unique needs of the local market, and adapt your products or services accordingly. 5. Price Sensitivity: Emerging markets are often price-sensitive, so it's essential to develop a pricing strategy that reflects the local market's purchasing power. 6. Build Trust:   […truncated…]</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="D22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I22" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D22:H22),D22:H22)), "")</f>
         <v/>
       </c>
-      <c r="J22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="360" customHeight="1">
+      <c r="J22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="409" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>65</t>
@@ -1813,18 +3136,32 @@
 6. Plagiarism check: Finally, we run the paper thr  […truncated…]</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
+      <c r="D23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I23" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D23:H23),D23:H23)), "")</f>
         <v/>
       </c>
-      <c r="J23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="360" customHeight="1">
+      <c r="J23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="409" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>78</t>
@@ -1851,18 +3188,32 @@
 In "A Legacy of Brilliance," the curtain rises on an illustrious family tree, spanning generations of theatrical excellence. With words that sing like sweet music, we are imbued with a sense of wonder at the magnificent tapestry of achievements woven by this royal lineage. Through evocative storytelling that plumbs the depths of human emotion, we are transported to a world of opulence and grandeur, where the magic of the stage and screen reigns supreme. In this chapter, we bear witness to the triumphs of those who came before, and the torchbearers who keep the flame of their genius burning bright. Theirs is a legacy of brilliance, one that inspires us to dream, to aspire, to reach for the stars. Through this chapter, we are reminded that true greatness endures, that it transcends time and space, that it lives on forever in the hearts and minds of those who are touched by its magic.</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
+      <c r="D24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I24" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D24:H24),D24:H24)), "")</f>
         <v/>
       </c>
-      <c r="J24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="360" customHeight="1">
+      <c r="J24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="409" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>67</t>
@@ -1911,18 +3262,30 @@
 Remember, however, that valuation metrics are only one aspect of a company's financial performance, and they should be interpreted in the context of other financial metrics, such as revenue growth, profit margins,  […truncated…]</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
+      <c r="D25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I25" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D25:H25),D25:H25)), "")</f>
         <v/>
       </c>
-      <c r="J25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26" ht="360" customHeight="1">
+      <c r="J25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="409" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>38</t>
@@ -1985,18 +3348,30 @@
 While the ability to book a massage using a smart building automation system may seem like a luxury or convenience, it can help improve employee well-being, promote relaxation and reduce stress, ultimately improving productivity and job satisfaction.</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
+      <c r="D26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I26" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D26:H26),D26:H26)), "")</f>
         <v/>
       </c>
-      <c r="J26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="360" customHeight="1">
+      <c r="J26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="409" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>51</t>
@@ -2034,18 +3409,32 @@
 Despite the turmoil around him, Tom did not lose hope. He drew upon his inner strength and perseverance to keep moving forward. Despite his shivering, he managed to k  […truncated…]</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
+      <c r="D27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I27" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D27:H27),D27:H27)), "")</f>
         <v/>
       </c>
-      <c r="J27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28" ht="360" customHeight="1">
+      <c r="J27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="409" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>90</t>
@@ -2111,18 +3500,32 @@
 ⭐ [New feature name] – Enjoy seamless [functionality] that is tailored to your unique needs and preferences. Our latest upgrade offers a range of customizable options that let you [add specific details on  […truncated…]</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
+      <c r="D28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I28" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D28:H28),D28:H28)), "")</f>
         <v/>
       </c>
-      <c r="J28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29" ht="360" customHeight="1">
+      <c r="J28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="409" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>8</t>
@@ -2197,18 +3600,30 @@
 5. Mixing: When making cocktails with your fat-washed bourbon, start with a small amount and adjust the pro  […truncated…]</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I29" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D29:H29),D29:H29)), "")</f>
         <v/>
       </c>
-      <c r="J29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30" ht="360" customHeight="1">
+      <c r="J29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="409" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>77</t>
@@ -2249,18 +3664,32 @@
 Remember, gratitude is not about pretending that everything is perfect or ignoring the difficult parts of life. It's about finding the small things to appreciate and focusing on   […truncated…]</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
+      <c r="D30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I30" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D30:H30),D30:H30)), "")</f>
         <v/>
       </c>
-      <c r="J30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31" ht="360" customHeight="1">
+      <c r="J30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="409" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>85</t>
@@ -2296,16 +3725,30 @@
 Most of the time, the hospital felt oppressively quiet, the stillness broken only by the soft sounds of footsteps and the occasional dull thud of doors closing. The silence was only ever broken by the occas  […truncated…]</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
+      <c r="D31" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I31" s="7">
         <f>IFERROR(AVERAGE(IF(ISNUMBER(D31:H31),D31:H31)), "")</f>
         <v/>
       </c>
-      <c r="J31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -2320,19 +3763,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="2" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
